--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6184-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6184-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E584C80A-67D9-4A14-9436-D1ED0DEC0F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{499799D1-F2FB-44F8-8B70-DF89E635292F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1EDD3CB7-F8BE-48EF-B20C-A14A3D3059B1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1B0FEBA3-7220-43EE-A6AB-E565F3CF7C7C}"/>
   </bookViews>
   <sheets>
     <sheet name="6184-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1475,25 +1475,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1914655-5092-4689-BCE5-D52E711796AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F2C30C-7687-4B30-B72F-9102E69CF4BD}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1521,7 +1521,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1647,7 +1647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2021</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2020</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2019</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2017</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2016</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2015</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2014</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2013</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2012</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2011</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2010</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2009</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2008</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2007</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2006</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2005</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2004</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2003</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2002</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2001</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
         <v>44</v>
       </c>
